--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente l'acteur System. </t>
+    <t>Cet attribut représente l'acteur System.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -231,7 +231,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: null</t>
+    <t>Mapping: ActorXDSCDA</t>
   </si>
   <si>
     <t/>
@@ -378,7 +378,7 @@
 </t>
   </si>
   <si>
-    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, • U, pour les systèmes.</t>
+    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, -U, pour les systèmes.</t>
   </si>
   <si>
     <t>U</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -278,7 +278,7 @@
     <t>ActorSystem.XCN1.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme}
+    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme|0.1.0}
 </t>
   </si>
   <si>
@@ -714,7 +714,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="76.48828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
